--- a/artfynd/A 10699-2025 artfynd.xlsx
+++ b/artfynd/A 10699-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129230029</v>
       </c>
       <c r="B2" t="n">
-        <v>98696</v>
+        <v>98706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10699-2025 artfynd.xlsx
+++ b/artfynd/A 10699-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129230029</v>
       </c>
       <c r="B2" t="n">
-        <v>98706</v>
+        <v>98713</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10699-2025 artfynd.xlsx
+++ b/artfynd/A 10699-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129230029</v>
       </c>
       <c r="B2" t="n">
-        <v>98713</v>
+        <v>98715</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10699-2025 artfynd.xlsx
+++ b/artfynd/A 10699-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129230029</v>
       </c>
       <c r="B2" t="n">
-        <v>98715</v>
+        <v>98741</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10699-2025 artfynd.xlsx
+++ b/artfynd/A 10699-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129230029</v>
       </c>
       <c r="B2" t="n">
-        <v>98741</v>
+        <v>98742</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10699-2025 artfynd.xlsx
+++ b/artfynd/A 10699-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129230029</v>
       </c>
       <c r="B2" t="n">
-        <v>98742</v>
+        <v>98743</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10699-2025 artfynd.xlsx
+++ b/artfynd/A 10699-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129230029</v>
       </c>
       <c r="B2" t="n">
-        <v>98743</v>
+        <v>98747</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10699-2025 artfynd.xlsx
+++ b/artfynd/A 10699-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129230029</v>
       </c>
       <c r="B2" t="n">
-        <v>98747</v>
+        <v>98749</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10699-2025 artfynd.xlsx
+++ b/artfynd/A 10699-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129230029</v>
       </c>
       <c r="B2" t="n">
-        <v>98749</v>
+        <v>98753</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10699-2025 artfynd.xlsx
+++ b/artfynd/A 10699-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129230029</v>
       </c>
       <c r="B2" t="n">
-        <v>98753</v>
+        <v>98761</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10699-2025 artfynd.xlsx
+++ b/artfynd/A 10699-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129230029</v>
       </c>
       <c r="B2" t="n">
-        <v>98761</v>
+        <v>98764</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10699-2025 artfynd.xlsx
+++ b/artfynd/A 10699-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129230029</v>
       </c>
       <c r="B2" t="n">
-        <v>98764</v>
+        <v>98793</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
